--- a/data/trans_dic/IP1002-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1002-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen bornquitis crónica</t>
+          <t>Menores que padecen bornquitis crónica (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,21</t>
+          <t>0,69; 6,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 6,19</t>
+          <t>0,68; 6,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,48</t>
+          <t>0,0; 4,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,28</t>
+          <t>0,0; 4,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 8,6</t>
+          <t>1,46; 8,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 7,55</t>
+          <t>0,79; 7,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,82</t>
+          <t>0,0; 4,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,13</t>
+          <t>0,0; 6,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,86</t>
+          <t>1,52; 6,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 5,57</t>
+          <t>1,39; 5,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,33</t>
+          <t>0,0; 3,05</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,19</t>
+          <t>0,0; 3,83</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,49</t>
+          <t>0,64; 2,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,95</t>
+          <t>0,79; 2,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,36</t>
+          <t>0,53; 2,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,47</t>
+          <t>0,58; 2,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,87</t>
+          <t>0,42; 1,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,77</t>
+          <t>1,48; 3,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,51</t>
+          <t>0,71; 2,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,93</t>
+          <t>0,61; 2,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,86</t>
+          <t>0,65; 1,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,94</t>
+          <t>1,42; 3,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,93</t>
+          <t>0,83; 2,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,2</t>
+          <t>0,78; 2,2</t>
         </is>
       </c>
     </row>
@@ -996,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,89</t>
+          <t>0,0; 2,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,45</t>
+          <t>0,0; 2,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,9</t>
+          <t>0,29; 2,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,92</t>
+          <t>0,39; 4,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1021,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,15</t>
+          <t>0,47; 4,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,71</t>
+          <t>0,35; 3,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,35</t>
+          <t>0,45; 4,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,8</t>
+          <t>0,19; 1,72</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,91</t>
+          <t>0,52; 2,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,36</t>
+          <t>0,5; 2,45</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,12</t>
+          <t>0,62; 3,13</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,2</t>
+          <t>0,73; 2,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,5</t>
+          <t>0,84; 2,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,84</t>
+          <t>0,57; 1,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,28</t>
+          <t>0,69; 2,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,97</t>
+          <t>0,67; 2,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,43</t>
+          <t>1,65; 3,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,23</t>
+          <t>0,8; 2,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,53</t>
+          <t>0,77; 2,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,87</t>
+          <t>0,89; 1,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,57</t>
+          <t>1,44; 2,63</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,77</t>
+          <t>0,84; 1,78</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,03</t>
+          <t>0,83; 2,0</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen bornquitis crónica (tasa de respuesta: 99,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2492</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2427</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3378</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2617</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>863</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>5869</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5044</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1251</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1254</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>628; 5631</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>625; 5736</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2943</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2423</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1270; 7471</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>656; 6324</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2837</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3873</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2694; 11121</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2430; 9615</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3899</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4467</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>5761</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7112</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5486</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5919</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4331</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>12199</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>6782</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>6941</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>10091</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>19311</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>12267</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2667; 11228</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3563; 12416</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2488; 10516</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2664; 11528</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1994; 9006</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>7279; 19360</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>3457; 12336</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>3151; 14756</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>5797; 16987</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>13373; 28368</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>7970; 20016</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>7571; 21434</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1331</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1238</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1664</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2387</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3071</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2608</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2145</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4309</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4273</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>5239</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4549</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4288</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>500; 5033</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>590; 6268</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4070</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>806; 7323</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>653; 6316</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>833; 8239</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>621; 5703</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1737; 9254</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1788; 8826</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2073; 10434</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>9584</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10777</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7714</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8698</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>8521</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>17887</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>10077</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>10656</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>18105</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>28664</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>17791</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>19354</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>4955; 14993</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>5958; 17024</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>3992; 12658</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>4599; 14672</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>4822; 14642</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>12321; 25975</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>5957; 16412</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>5837; 18656</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>12551; 26760</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>20894; 38247</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>12131; 25866</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>11859; 28480</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1002-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1002-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,2</t>
+          <t>0,69; 6,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,24</t>
+          <t>0,68; 6,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,96</t>
+          <t>0,0; 5,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,43</t>
+          <t>0,0; 4,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 8,6</t>
+          <t>1,48; 7,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 7,57</t>
+          <t>0,84; 8,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,14</t>
+          <t>0,0; 5,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,25</t>
+          <t>0,0; 9,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 6,26</t>
+          <t>1,73; 6,16</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 5,48</t>
+          <t>1,36; 5,49</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,05</t>
+          <t>0,0; 3,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,83</t>
+          <t>0,0; 3,92</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,7</t>
+          <t>0,7; 2,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,76</t>
+          <t>0,76; 2,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,23</t>
+          <t>0,52; 2,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,51</t>
+          <t>0,56; 2,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,89</t>
+          <t>0,33; 1,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,93</t>
+          <t>1,53; 3,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,52</t>
+          <t>0,7; 2,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,86</t>
+          <t>0,53; 2,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,9</t>
+          <t>0,66; 1,85</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,01</t>
+          <t>1,38; 2,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,08</t>
+          <t>0,77; 1,98</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,2</t>
+          <t>0,77; 2,28</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,59</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,91</t>
+          <t>0,29; 2,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,19</t>
+          <t>0,39; 4,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,27</t>
+          <t>0,46; 4,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,37</t>
+          <t>0,34; 3,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,49</t>
+          <t>0,0; 4,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,72</t>
+          <t>0,19; 1,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,75</t>
+          <t>0,52; 2,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,45</t>
+          <t>0,49; 2,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,13</t>
+          <t>0,61; 3,29</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,2</t>
+          <t>0,82; 2,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,41</t>
+          <t>0,91; 2,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,8</t>
+          <t>0,59; 1,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,21</t>
+          <t>0,75; 2,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,03</t>
+          <t>0,67; 2,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,47</t>
+          <t>1,61; 3,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,2</t>
+          <t>0,82; 2,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,45</t>
+          <t>0,75; 2,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,91</t>
+          <t>0,88; 1,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,63</t>
+          <t>1,43; 2,64</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,78</t>
+          <t>0,8; 1,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,0</t>
+          <t>0,86; 2,05</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>628; 5631</t>
+          <t>628; 6312</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>625; 5736</t>
+          <t>625; 5924</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2943</t>
+          <t>0; 3155</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2423</t>
+          <t>0; 2273</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1270; 7471</t>
+          <t>1283; 6823</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>656; 6324</t>
+          <t>704; 7223</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2837</t>
+          <t>0; 3911</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3873</t>
+          <t>0; 5619</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2694; 11121</t>
+          <t>3072; 10943</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2430; 9615</t>
+          <t>2390; 9631</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 3899</t>
+          <t>0; 4261</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 4467</t>
+          <t>0; 4575</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2667; 11228</t>
+          <t>2898; 10696</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3563; 12416</t>
+          <t>3411; 12318</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2488; 10516</t>
+          <t>2447; 10547</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2664; 11528</t>
+          <t>2582; 11923</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1994; 9006</t>
+          <t>1592; 9191</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7279; 19360</t>
+          <t>7547; 18412</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3457; 12336</t>
+          <t>3409; 12003</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3151; 14756</t>
+          <t>2738; 13566</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5797; 16987</t>
+          <t>5911; 16486</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13373; 28368</t>
+          <t>13046; 27244</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7970; 20016</t>
+          <t>7392; 19028</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7571; 21434</t>
+          <t>7483; 22235</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4549</t>
+          <t>0; 4700</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4288</t>
+          <t>0; 4245</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>500; 5033</t>
+          <t>502; 4490</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>590; 6268</t>
+          <t>579; 6021</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4070</t>
+          <t>0; 4041</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>806; 7323</t>
+          <t>784; 7350</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>653; 6316</t>
+          <t>643; 6370</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>833; 8239</t>
+          <t>0; 7526</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>621; 5703</t>
+          <t>625; 6218</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1737; 9254</t>
+          <t>1742; 9139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1788; 8826</t>
+          <t>1769; 8856</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2073; 10434</t>
+          <t>2041; 10957</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4955; 14993</t>
+          <t>5571; 15385</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5958; 17024</t>
+          <t>6422; 17518</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3992; 12658</t>
+          <t>4151; 13589</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4599; 14672</t>
+          <t>4961; 14995</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4822; 14642</t>
+          <t>4871; 14819</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12321; 25975</t>
+          <t>12072; 25514</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5957; 16412</t>
+          <t>6091; 16307</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5837; 18656</t>
+          <t>5675; 19366</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12551; 26760</t>
+          <t>12375; 26104</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20894; 38247</t>
+          <t>20828; 38383</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12131; 25866</t>
+          <t>11636; 25341</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11859; 28480</t>
+          <t>12235; 29188</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1002-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1002-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2,74%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,64%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,95%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -717,52 +717,52 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,95</t>
+          <t>1,48; 8,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,45</t>
+          <t>0,79; 7,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,31</t>
+          <t>0,0; 5,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,16</t>
+          <t>0,0; 9,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 7,86</t>
+          <t>0,7; 6,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 8,65</t>
+          <t>0,67; 6,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,7</t>
+          <t>0,0; 4,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,06</t>
+          <t>0,0; 4,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 6,16</t>
+          <t>1,48; 5,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,49</t>
+          <t>1,34; 5,57</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,92</t>
+          <t>0,0; 4,9</t>
         </is>
       </c>
     </row>
@@ -789,62 +789,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>1,38%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,58%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>1,16%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>1,39%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>1,35%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,57</t>
+          <t>0,29; 1,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,74</t>
+          <t>1,4; 3,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,23</t>
+          <t>0,71; 2,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,59</t>
+          <t>0,61; 3,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,93</t>
+          <t>0,64; 2,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,74</t>
+          <t>0,77; 2,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,46</t>
+          <t>0,51; 2,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,63</t>
+          <t>0,66; 2,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,85</t>
+          <t>0,67; 1,86</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,89</t>
+          <t>1,4; 2,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,98</t>
+          <t>0,73; 1,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,28</t>
+          <t>0,73; 2,23</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>0,76%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,75%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,96%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,7</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>0,55; 4,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,6</t>
+          <t>0,35; 3,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,03</t>
+          <t>0,51; 4,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,28</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,4</t>
+          <t>0,29; 2,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,1</t>
+          <t>0,35; 3,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,87</t>
+          <t>0,19; 1,8</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,71</t>
+          <t>0,59; 2,91</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,46</t>
+          <t>0,5; 2,36</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,29</t>
+          <t>0,6; 3,12</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1,41%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,26</t>
+          <t>0,66; 1,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,48</t>
+          <t>1,59; 3,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,93</t>
+          <t>0,81; 2,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,26</t>
+          <t>0,72; 2,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,05</t>
+          <t>0,76; 2,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,41</t>
+          <t>0,91; 2,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,19</t>
+          <t>0,54; 1,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,54</t>
+          <t>0,74; 2,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,86</t>
+          <t>0,87; 1,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,64</t>
+          <t>1,45; 2,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,75</t>
+          <t>0,85; 1,77</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,05</t>
+          <t>0,9; 2,06</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,27 +1368,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3378</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2617</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>2492</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2427</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>564</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3378</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2617</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>340</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1237</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>628; 6312</t>
+          <t>1289; 7469</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>625; 5924</t>
+          <t>662; 6304</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3155</t>
+          <t>0; 3994</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2273</t>
+          <t>0; 5312</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1283; 6823</t>
+          <t>635; 5642</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>704; 7223</t>
+          <t>616; 5688</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3911</t>
+          <t>0; 2662</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5619</t>
+          <t>0; 2092</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3072; 10943</t>
+          <t>2630; 10406</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2390; 9631</t>
+          <t>2355; 9780</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 4261</t>
+          <t>0; 4262</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 4575</t>
+          <t>0; 5070</t>
         </is>
       </c>
     </row>
@@ -1576,37 +1576,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4331</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12199</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6782</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6208</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5761</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>7112</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>5486</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5919</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4331</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12199</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6782</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>12219</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2898; 10696</t>
+          <t>1406; 8896</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3411; 12318</t>
+          <t>6909; 18542</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2447; 10547</t>
+          <t>3460; 12272</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2582; 11923</t>
+          <t>2896; 14335</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1592; 9191</t>
+          <t>2656; 10346</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7547; 18412</t>
+          <t>3465; 13259</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3409; 12003</t>
+          <t>2407; 11150</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2738; 13566</t>
+          <t>2870; 11434</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5911; 16486</t>
+          <t>5977; 16636</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13046; 27244</t>
+          <t>13173; 27697</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7392; 19028</t>
+          <t>7061; 18567</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7483; 22235</t>
+          <t>6583; 20205</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3071</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2608</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2771</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1331</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1238</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1664</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2387</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>3071</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2608</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>2276</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5239</t>
+          <t>5047</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4700</t>
+          <t>0; 4065</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4245</t>
+          <t>941; 7116</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>502; 4490</t>
+          <t>655; 6955</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>579; 6021</t>
+          <t>861; 7489</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4041</t>
+          <t>0; 5030</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>784; 7350</t>
+          <t>0; 4048</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>643; 6370</t>
+          <t>502; 5001</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 7526</t>
+          <t>524; 5760</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>625; 6218</t>
+          <t>624; 5972</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1742; 9139</t>
+          <t>1991; 9803</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1769; 8856</t>
+          <t>1791; 8507</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2041; 10957</t>
+          <t>1906; 9942</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>8521</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>17887</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10077</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9876</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>9584</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>10777</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>7714</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8698</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>8521</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>17887</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>10077</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>8628</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19354</t>
+          <t>18504</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5571; 15385</t>
+          <t>4777; 14230</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6422; 17518</t>
+          <t>11868; 25630</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4151; 13589</t>
+          <t>6040; 16584</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4961; 14995</t>
+          <t>5041; 17203</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4871; 14819</t>
+          <t>5199; 14993</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12072; 25514</t>
+          <t>6421; 17680</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6091; 16307</t>
+          <t>3827; 12962</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5675; 19366</t>
+          <t>4619; 14939</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12375; 26104</t>
+          <t>12167; 26293</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20828; 38383</t>
+          <t>21081; 37320</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11636; 25341</t>
+          <t>12253; 25723</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12235; 29188</t>
+          <t>11927; 27370</t>
         </is>
       </c>
     </row>
